--- a/ksoft/docs/records/Currency.xlsx
+++ b/ksoft/docs/records/Currency.xlsx
@@ -1495,13 +1495,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AC3BD46-51B3-47E7-A09F-F608E5399D0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5F3FC98-741E-4169-90F4-7D7BEC08E843}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C99FBFEA-5A61-4747-913D-517D11F962C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B177E5EA-F298-4AF0-96CE-9BCCDDE113A8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4571B4BE-8B72-4A6A-A1D4-98C436741DF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37E09C7D-4E01-40B1-A11F-F8F79C1FD7BC}"/>
 </file>
--- a/ksoft/docs/records/Currency.xlsx
+++ b/ksoft/docs/records/Currency.xlsx
@@ -1495,13 +1495,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5F3FC98-741E-4169-90F4-7D7BEC08E843}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AC3BD46-51B3-47E7-A09F-F608E5399D0B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B177E5EA-F298-4AF0-96CE-9BCCDDE113A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C99FBFEA-5A61-4747-913D-517D11F962C0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37E09C7D-4E01-40B1-A11F-F8F79C1FD7BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4571B4BE-8B72-4A6A-A1D4-98C436741DF2}"/>
 </file>